--- a/data/externalStats/File1/RPT_RPT9073295656307CV_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT9073295656307CV_externalStats.xlsx
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>9409336.353308462</v>
+        <v>3641384.037658073</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>37842.22928475848</v>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>3672349.711338458</v>
+        <v>1421187.968784233</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>14824.51869790836</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>3376831.917632935</v>
+        <v>1306823.497535965</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>12396.8159518388</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1701127.450941039</v>
+        <v>658331.0568657274</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>953567.7123956345</v>
+        <v>369027.7524750907</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>2997.03719227378</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>890886.5802619979</v>
+        <v>344770.348398606</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>0</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>697287.2441386321</v>
+        <v>269848.004697613</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>5564.442124999997</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>644927.5254599275</v>
+        <v>249584.9556733465</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>2057.340789</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>594511.6609354606</v>
+        <v>230074.1721886458</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>2313.128836677755</v>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>587575.9526771638</v>
+        <v>227390.0745654659</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>307.2083568587134</v>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>516140.8095778506</v>
+        <v>199744.8953474654</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3118.807607</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>468079.4587212444</v>
+        <v>181145.3013627107</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>1821.671488505162</v>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>431408.612285597</v>
+        <v>166953.7973241475</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>2216.344193326221</v>
+        <v>2216.34419332622</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>422455.7911595696</v>
+        <v>163489.0832660873</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>399322.1943800783</v>
+        <v>154536.4529334668</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>1336.815113562571</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>371975.5615620323</v>
+        <v>143953.3906973809</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>2577.615379373739</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>343865.7988222653</v>
+        <v>133074.9995442203</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>1651.013328294838</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>330745.2511201117</v>
+        <v>127997.3882043776</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>287712.22972371</v>
+        <v>111343.7421531386</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>1223.024059400763</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>275970.9625213675</v>
+        <v>106799.9080965045</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>39.393095</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>14080285.68507328</v>
+        <v>5449026.967907615</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>56332.87391490716</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>3698121.481174404</v>
+        <v>1431161.563921983</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>13552.8868498282</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>2846351.934100889</v>
+        <v>1101529.386261954</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>10927.10418072</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>2752448.524341527</v>
+        <v>1065189.057407712</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>0</v>
@@ -3905,13 +3905,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.064847128097</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450652</v>
+        <v>790.7877512450654</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -3920,13 +3920,13 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.838043207603</v>
+        <v>3021.838043207602</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.9119035695702</v>
+        <v>757.9119035695699</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -3938,16 +3938,16 @@
         <v>5957.504189498098</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.086637895055</v>
+        <v>2933.086637895057</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.2309046434759</v>
+        <v>729.2309046434757</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.821732036629</v>
+        <v>9619.821732036631</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>1157516.413403158</v>
+        <v>447955.2683448753</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>4942.766476981106</v>
@@ -3992,7 +3992,7 @@
         <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -4007,7 +4007,7 @@
         <v>8427.448628435308</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>847467.9434636511</v>
+        <v>327967.4703806699</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>6705.229304216664</v>
@@ -4067,13 +4067,13 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -4085,25 +4085,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>682265.8471587867</v>
+        <v>264034.7705722859</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>559.6304546400543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>548895.1877735461</v>
+        <v>212420.7383024559</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>5166.812702887033</v>
@@ -4244,34 +4244,34 @@
         <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571055</v>
+        <v>6533.070130571056</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860723</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295336</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961312</v>
+        <v>8093.670157961314</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>429.0106540106552</v>
+        <v>429.0106540106551</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8230.488366920139</v>
+        <v>8230.488366920141</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>457843.8719691203</v>
+        <v>177184.1609787617</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>393215.6631150934</v>
+        <v>152173.2442395872</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>2716.700648453738</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>330745.2511201116</v>
+        <v>127997.3882043776</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>0</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>328578.7497241422</v>
+        <v>127158.958871572</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>2740.1603206045</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>290935.50366326</v>
+        <v>112591.1391885681</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>2705.748534253712</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>235290.1677033459</v>
+        <v>91056.56644866327</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>496.7672586372211</v>
@@ -4715,10 +4715,10 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.13541467506</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>607.4898571432227</v>
@@ -4727,37 +4727,37 @@
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305863</v>
+        <v>30105.74160305862</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966782</v>
+        <v>5875.167457966767</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.7844878750766</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326458</v>
+        <v>32703.15220326457</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6144.224276925182</v>
+        <v>6144.224276925168</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1767.142052340065</v>
+        <v>1767.142052340063</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>655.1214664631962</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>35693.26246439303</v>
+        <v>35693.26246439302</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>161198.5395832641</v>
+        <v>62383.3357520372</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>1877.738034182704</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>127856.4170618569</v>
+        <v>49480.03756263811</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>2064.596372658817</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>117905.0266126316</v>
+        <v>45628.88026804629</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>420.26223104</v>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>116652.8953777721</v>
+        <v>45144.30935672296</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>713.0440565881274</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>96122.43022321824</v>
+        <v>37199.08290372223</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>328.1647160000001</v>
@@ -5156,7 +5156,7 @@
         <v>123126.4610400058</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56400.30057805718</v>
+        <v>56400.30057805717</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15913.04608529102</v>
@@ -5165,7 +5165,7 @@
         <v>5035.70598772958</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>131602.601988407</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>99630.84520604849</v>
+        <v>38556.82864011164</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>927.3717440000001</v>
@@ -5336,7 +5336,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998419</v>
+        <v>6291.051318998418</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215568</v>
+        <v>7755.955719215567</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6402.12610667536</v>
@@ -5363,10 +5363,10 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.85128299104</v>
+        <v>7908.851282991039</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169954</v>
+        <v>6480.947150169952</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283766</v>
+        <v>8025.240261283764</v>
       </c>
     </row>
     <row r="72">
@@ -5421,7 +5421,7 @@
         <v>3.034850177968129</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.99935879958163</v>
+        <v>0.9993587995816298</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -5604,13 +5604,13 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.409122198132</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174763</v>
+        <v>2374.418161174764</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>535.5877718652724</v>
+        <v>535.5877718652725</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
         <v>8643.557255466281</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.307259689338</v>
+        <v>2736.307259689339</v>
       </c>
       <c r="R75" s="131" t="n">
         <v>615.2216261623436</v>
@@ -5634,13 +5634,13 @@
         <v>11995.08614131796</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9438.884141585027</v>
+        <v>9438.884141585026</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058534</v>
+        <v>680.2887679058531</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
@@ -6006,25 +6006,25 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731803</v>
+        <v>2908.033523731805</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580813</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083913</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.196203083917</v>
       </c>
     </row>
     <row r="82">
@@ -6387,7 +6387,7 @@
         <v>3567.196203083913</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>28545.99954209993</v>
+        <v>28545.99954209994</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -6559,7 +6559,7 @@
         <v>12526.95646477333</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.671517703221</v>
+        <v>4162.67151770322</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.803605389631</v>
@@ -6574,7 +6574,7 @@
         <v>12438.45133966805</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.197362555249</v>
+        <v>4104.197362555251</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.413291097094</v>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17645.0619933204</v>
+        <v>17645.06199332039</v>
       </c>
     </row>
     <row r="90">
@@ -6614,7 +6614,7 @@
         <v>7846.477550993603</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>8428.447987234889</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -6675,13 +6675,13 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -6693,25 +6693,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -6745,7 +6745,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -6760,7 +6760,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -6809,10 +6809,10 @@
         <v>16156</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>14334.76693728304</v>
+        <v>14334.76693728303</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.617170974005</v>
+        <v>3581.617170974007</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>982.7439641763199</v>
@@ -6842,10 +6842,10 @@
         <v>16093.06882680675</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4194.572762452257</v>
+        <v>4194.572762452259</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1109.299421916509</v>
+        <v>1109.299421916508</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>25314</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -7223,22 +7223,22 @@
         <v>25112.75664481348</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>33013.77512679044</v>
+        <v>33013.77512679042</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5875.167457966789</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>629.7844878750775</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>27728.22190465722</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>35937.1267708454</v>
+        <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6144.224276925175</v>
@@ -7553,7 +7553,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -7577,7 +7577,7 @@
         <v>27728.22190465722</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>149710.8391798171</v>
+        <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72515.58812458278</v>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>12596510.61370243</v>
+        <v>4992519.450552792</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>47681.20374516815</v>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>3980344.760658169</v>
+        <v>1577575.66733403</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>13973.95203328434</v>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>3811644.453422499</v>
+        <v>1510712.740685746</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>14231.53794999202</v>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1882446.706787872</v>
+        <v>746091.6825683637</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>1118948.373955205</v>
+        <v>443485.6360188311</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>3238.95803443412</v>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>962413.2162176404</v>
+        <v>381444.2625252843</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>0</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>770217.2416530458</v>
+        <v>305269.0287039511</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>2223.40933748808</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>702260.5615890891</v>
+        <v>278334.9786786024</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>334.5483687503169</v>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>618585.1088205444</v>
+        <v>245170.9272764352</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>0</v>
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>604876.5698440056</v>
+        <v>239737.6648771973</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>2220.603683210645</v>
+        <v>2220.603683210644</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>579169.0376467911</v>
+        <v>229548.7039453745</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3262.52226153056</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>561295.3629099766</v>
+        <v>222464.6255435882</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>1968.716811057299</v>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>512220.0016371177</v>
+        <v>203014.0250391015</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>2395.247496611513</v>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>414468.7589632028</v>
+        <v>164271.154467123</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>1283.342509020068</v>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>408521.432658471</v>
+        <v>161913.9824561013</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>2706.758133649526</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>399585.376429092</v>
+        <v>158372.2528529938</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>1784.283124154797</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>354493.1917173238</v>
+        <v>140500.3503757685</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>0</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>302040.390869187</v>
+        <v>119711.1305274217</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>41.20832881760001</v>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>298235.5486730942</v>
+        <v>118203.1138033605</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>1167.523227585156</v>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>270577.0729080788</v>
+        <v>107240.9130428361</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>1698.80191375</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>17432475.46232843</v>
+        <v>6909212.835678951</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>65432.22259011088</v>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>4372525.364131154</v>
+        <v>1733013.101637348</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>15269.46720757884</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>3367528.818743662</v>
+        <v>1334691.300111817</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>11809.14003018772</v>
@@ -10401,7 +10401,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>3018765.245957789</v>
+        <v>1196461.835288148</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>0</v>
@@ -10429,13 +10429,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.064847128097</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450652</v>
+        <v>790.7877512450654</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -10444,13 +10444,13 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.838043207603</v>
+        <v>3021.838043207602</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.9119035695702</v>
+        <v>757.9119035695699</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -10462,16 +10462,16 @@
         <v>5957.504189498098</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.086637895055</v>
+        <v>2933.086637895057</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.2309046434759</v>
+        <v>729.2309046434757</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.821732036629</v>
+        <v>9619.821732036631</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>1290499.002814001</v>
+        <v>511478.2633104271</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>5170.529156240395</v>
@@ -10516,7 +10516,7 @@
         <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -10531,7 +10531,7 @@
         <v>8427.448628435308</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -10563,10 +10563,10 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>811536.9252784462</v>
+        <v>321645.732579872</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>589.6962984580065</v>
+        <v>589.6962984580066</v>
       </c>
     </row>
     <row r="55">
@@ -10591,13 +10591,13 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -10609,25 +10609,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>671914.9728780718</v>
+        <v>266307.7636406992</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>0</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>570057.9987221956</v>
+        <v>225937.6214447727</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>4932.342742430019</v>
@@ -10768,34 +10768,34 @@
         <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571055</v>
+        <v>6533.070130571056</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860723</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295336</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961312</v>
+        <v>8093.670157961314</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>429.0106540106552</v>
+        <v>429.0106540106551</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8230.488366920139</v>
+        <v>8230.488366920141</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>433301.2174640478</v>
+        <v>171735.2386290433</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>2854.153747557056</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>382021.5040799764</v>
+        <v>151410.9619829174</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>2939.919686845487</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>354493.1917173237</v>
+        <v>140500.3503757686</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>0</v>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>290360.8559341815</v>
+        <v>115082.0465592793</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>2582.961665769278</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>262890.6363215882</v>
+        <v>104194.4595177026</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>512.3210415051525</v>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>184707.9880123315</v>
+        <v>73207.43427318014</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>2455.880032873868</v>
@@ -11239,10 +11239,10 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.13541467506</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>607.4898571432227</v>
@@ -11251,37 +11251,37 @@
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305863</v>
+        <v>30105.74160305862</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966782</v>
+        <v>5875.167457966767</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.7844878750766</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326458</v>
+        <v>32703.15220326457</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6144.224276925182</v>
+        <v>6144.224276925168</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1767.142052340065</v>
+        <v>1767.142052340063</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>655.1214664631962</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>35693.26246439303</v>
+        <v>35693.26246439302</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>157014.2618141267</v>
+        <v>62231.26230437949</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>1705.267795743023</v>
@@ -11359,10 +11359,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>148615.2194929604</v>
+        <v>58902.373579527</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>2182.219801634688</v>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>131766.0204378066</v>
+        <v>52224.33736864285</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>431.8698738613248</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>123836.3205313705</v>
+        <v>49081.4685032871</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>387.2343648800002</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>123296.3557552961</v>
+        <v>48867.45807374539</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>704.1345029771253</v>
@@ -11680,7 +11680,7 @@
         <v>123126.4610400058</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56400.30057805718</v>
+        <v>56400.30057805717</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15913.04608529102</v>
@@ -11689,7 +11689,7 @@
         <v>5035.70598772958</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>131602.601988407</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>106437.1740130658</v>
+        <v>42185.46531005655</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>924.74728196448</v>
@@ -11860,7 +11860,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998419</v>
+        <v>6291.051318998418</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
@@ -11872,7 +11872,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215568</v>
+        <v>7755.955719215567</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6402.12610667536</v>
@@ -11887,10 +11887,10 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.85128299104</v>
+        <v>7908.851282991039</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169954</v>
+        <v>6480.947150169952</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
@@ -11902,7 +11902,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283766</v>
+        <v>8025.240261283764</v>
       </c>
     </row>
     <row r="72">
@@ -11945,7 +11945,7 @@
         <v>3.034850177968129</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.99935879958163</v>
+        <v>0.9993587995816298</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -12064,7 +12064,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -12079,7 +12079,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -12128,13 +12128,13 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.409122198132</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174763</v>
+        <v>2374.418161174764</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>535.5877718652724</v>
+        <v>535.5877718652725</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>0</v>
@@ -12146,7 +12146,7 @@
         <v>8643.557255466281</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.307259689338</v>
+        <v>2736.307259689339</v>
       </c>
       <c r="R75" s="131" t="n">
         <v>615.2216261623436</v>
@@ -12158,13 +12158,13 @@
         <v>11995.08614131796</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9438.884141585027</v>
+        <v>9438.884141585026</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058534</v>
+        <v>680.2887679058531</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
@@ -12530,25 +12530,25 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731803</v>
+        <v>2908.033523731805</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -12557,22 +12557,22 @@
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580813</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083913</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.196203083917</v>
       </c>
     </row>
     <row r="82">
@@ -12911,7 +12911,7 @@
         <v>3567.196203083913</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>28545.99954209993</v>
+        <v>28545.99954209994</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -13083,7 +13083,7 @@
         <v>12526.95646477333</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.671517703221</v>
+        <v>4162.67151770322</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.803605389631</v>
@@ -13098,7 +13098,7 @@
         <v>12438.45133966805</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.197362555249</v>
+        <v>4104.197362555251</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.413291097094</v>
@@ -13107,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17645.0619933204</v>
+        <v>17645.06199332039</v>
       </c>
     </row>
     <row r="90">
@@ -13138,7 +13138,7 @@
         <v>7846.477550993603</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
@@ -13153,7 +13153,7 @@
         <v>8428.447987234889</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -13199,13 +13199,13 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -13217,25 +13217,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -13269,7 +13269,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -13284,7 +13284,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -13333,10 +13333,10 @@
         <v>16156</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>14334.76693728304</v>
+        <v>14334.76693728303</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.617170974005</v>
+        <v>3581.617170974007</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>982.7439641763199</v>
@@ -13366,10 +13366,10 @@
         <v>16093.06882680675</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4194.572762452257</v>
+        <v>4194.572762452259</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1109.299421916509</v>
+        <v>1109.299421916508</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -13735,10 +13735,10 @@
         <v>25314</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -13747,22 +13747,22 @@
         <v>25112.75664481348</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>33013.77512679044</v>
+        <v>33013.77512679042</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5875.167457966789</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>629.7844878750775</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>27728.22190465722</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>35937.1267708454</v>
+        <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6144.224276925175</v>
@@ -14077,7 +14077,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -14101,7 +14101,7 @@
         <v>27728.22190465722</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>149710.8391798171</v>
+        <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72515.58812458278</v>
@@ -15149,10 +15149,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>15956578.0947185</v>
+        <v>6468883.011372362</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>57217.44053621584</v>
+        <v>57217.44053621583</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15226,7 +15226,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>4680754.866784699</v>
+        <v>1897603.324372176</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>15724.71578175683</v>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>3921711.006263642</v>
+        <v>1589882.840377152</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>13662.27643199234</v>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>2062054.176739685</v>
+        <v>835967.9094890615</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>0</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>1298233.676414271</v>
+        <v>526310.9498976773</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>3491.467202798604</v>
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>1030612.94129414</v>
+        <v>417816.0572814081</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>906498.2427215438</v>
+        <v>367499.287589815</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>2396.746329438651</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>905061.8093026147</v>
+        <v>366916.9497172763</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>0</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>844310.3620731449</v>
+        <v>342287.9846242479</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>366.7694935161618</v>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>663668.3165240465</v>
+        <v>269054.722915154</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>2122.197973647326</v>
@@ -15899,10 +15899,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>649385.7192910649</v>
+        <v>263264.4807936749</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>3412.859287341889</v>
+        <v>3412.859287341888</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>613120.0409082349</v>
+        <v>248562.1787465817</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>2131.779535882219</v>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>606209.9805137323</v>
+        <v>245760.8029109726</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>2581.980991447345</v>
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>459107.617366803</v>
+        <v>186124.7097432986</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>1923.385836513905</v>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>426437.1227801543</v>
+        <v>172879.9146406031</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>1232.008808659265</v>
@@ -16260,7 +16260,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>379649.1568263823</v>
+        <v>153911.8203350199</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>0</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>330309.7816919024</v>
+        <v>133909.3709561766</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>43.10720860951501</v>
@@ -16414,7 +16414,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>311976.5815052453</v>
+        <v>126476.9925021265</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>1826.21205728125</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>307935.1218139796</v>
+        <v>124838.5628975593</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>1114.37757026548</v>
@@ -16568,10 +16568,10 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>305827.8299061272</v>
+        <v>123984.2553673489</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>828.6349090366573</v>
+        <v>828.6349090366574</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>20922985.84976449</v>
+        <v>8482291.560715334</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>74258.41862736085</v>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>5158238.390339103</v>
+        <v>2091177.72581315</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>17181.55579256998</v>
@@ -16804,7 +16804,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>3939800.149397455</v>
+        <v>1597216.276782752</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>12729.78058694115</v>
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>3279505.289433938</v>
+        <v>1329529.171392137</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>0</v>
@@ -16953,13 +16953,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.064847128097</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450652</v>
+        <v>790.7877512450654</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -16968,13 +16968,13 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.838043207603</v>
+        <v>3021.838043207602</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.9119035695702</v>
+        <v>757.9119035695699</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -16986,16 +16986,16 @@
         <v>5957.504189498098</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.086637895055</v>
+        <v>2933.086637895057</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.2309046434759</v>
+        <v>729.2309046434757</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.821732036629</v>
+        <v>9619.821732036631</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>1437194.644019877</v>
+        <v>582646.4773053555</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>5408.787139759954</v>
@@ -17040,7 +17040,7 @@
         <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -17055,7 +17055,7 @@
         <v>8427.448628435308</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>985358.4536487528</v>
+        <v>399469.643371116</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>0</v>
@@ -17115,13 +17115,13 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -17133,25 +17133,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>970964.2968182452</v>
+        <v>393634.1743857751</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>623.762204802456</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>585479.5305592752</v>
+        <v>237356.5664429494</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>4707.822500794605</v>
@@ -17292,34 +17292,34 @@
         <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571055</v>
+        <v>6533.070130571056</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860723</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295336</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961312</v>
+        <v>8093.670157961314</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>429.0106540106552</v>
+        <v>429.0106540106551</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8230.488366920139</v>
+        <v>8230.488366920141</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>379649.1568263823</v>
+        <v>153911.8203350199</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>0</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>311976.5815052453</v>
+        <v>126476.9925021265</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>2371.245811243431</v>
@@ -17492,7 +17492,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>292886.5114254815</v>
+        <v>118737.7749022222</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>527.7572744857026</v>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>289756.065414228</v>
+        <v>117468.6751679303</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>2465.38525074346</v>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>170144.0073098778</v>
+        <v>68977.30026076129</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>2302.200793744382</v>
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>158999.8974800146</v>
+        <v>64459.4178973032</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>456.9365505584</v>
@@ -17763,10 +17763,10 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.13541467506</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>607.4898571432227</v>
@@ -17775,37 +17775,37 @@
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305863</v>
+        <v>30105.74160305862</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966782</v>
+        <v>5875.167457966767</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.7844878750766</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326458</v>
+        <v>32703.15220326457</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6144.224276925182</v>
+        <v>6144.224276925168</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1767.142052340065</v>
+        <v>1767.142052340063</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>655.1214664631962</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>35693.26246439303</v>
+        <v>35693.26246439302</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>153479.8711383814</v>
+        <v>62221.56938042488</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>1554.334543141808</v>
@@ -17883,10 +17883,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -17897,10 +17897,10 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>153416.0293076598</v>
+        <v>62195.68755715938</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>1540.734713659511</v>
+        <v>1540.734713659512</v>
       </c>
     </row>
     <row r="65">
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>135063.4038542703</v>
+        <v>54755.43399497442</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>414.2063040845648</v>
@@ -18065,10 +18065,10 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>134506.6171015097</v>
+        <v>54529.70963574718</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>715.1447598447631</v>
+        <v>715.1447598447633</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>113236.5441883962</v>
+        <v>45906.70710340388</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>920.2992475382306</v>
+        <v>920.2992475382305</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -18204,7 +18204,7 @@
         <v>123126.4610400058</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56400.30057805718</v>
+        <v>56400.30057805717</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15913.04608529102</v>
@@ -18213,7 +18213,7 @@
         <v>5035.70598772958</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>131602.601988407</v>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>95956.66562390393</v>
+        <v>38901.3509286097</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>425.6180676129507</v>
@@ -18384,7 +18384,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998419</v>
+        <v>6291.051318998418</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
@@ -18396,7 +18396,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215568</v>
+        <v>7755.955719215567</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6402.12610667536</v>
@@ -18411,10 +18411,10 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.85128299104</v>
+        <v>7908.851282991039</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169954</v>
+        <v>6480.947150169952</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
@@ -18426,7 +18426,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283766</v>
+        <v>8025.240261283764</v>
       </c>
     </row>
     <row r="72">
@@ -18469,7 +18469,7 @@
         <v>3.034850177968129</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.99935879958163</v>
+        <v>0.9993587995816298</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -18588,7 +18588,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -18603,7 +18603,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -18652,13 +18652,13 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.409122198132</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174763</v>
+        <v>2374.418161174764</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>535.5877718652724</v>
+        <v>535.5877718652725</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>0</v>
@@ -18670,7 +18670,7 @@
         <v>8643.557255466281</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.307259689338</v>
+        <v>2736.307259689339</v>
       </c>
       <c r="R75" s="131" t="n">
         <v>615.2216261623436</v>
@@ -18682,13 +18682,13 @@
         <v>11995.08614131796</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9438.884141585027</v>
+        <v>9438.884141585026</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058534</v>
+        <v>680.2887679058531</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
@@ -19054,25 +19054,25 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731803</v>
+        <v>2908.033523731805</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -19081,22 +19081,22 @@
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580813</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083913</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.196203083917</v>
       </c>
     </row>
     <row r="82">
@@ -19435,7 +19435,7 @@
         <v>3567.196203083913</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>28545.99954209993</v>
+        <v>28545.99954209994</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -19607,7 +19607,7 @@
         <v>12526.95646477333</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.671517703221</v>
+        <v>4162.67151770322</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.803605389631</v>
@@ -19622,7 +19622,7 @@
         <v>12438.45133966805</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.197362555249</v>
+        <v>4104.197362555251</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.413291097094</v>
@@ -19631,7 +19631,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17645.0619933204</v>
+        <v>17645.06199332039</v>
       </c>
     </row>
     <row r="90">
@@ -19662,7 +19662,7 @@
         <v>7846.477550993603</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
@@ -19677,7 +19677,7 @@
         <v>8428.447987234889</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -19723,13 +19723,13 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -19741,25 +19741,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -19793,7 +19793,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -19808,7 +19808,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -19857,10 +19857,10 @@
         <v>16156</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>14334.76693728304</v>
+        <v>14334.76693728303</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.617170974005</v>
+        <v>3581.617170974007</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>982.7439641763199</v>
@@ -19890,10 +19890,10 @@
         <v>16093.06882680675</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4194.572762452257</v>
+        <v>4194.572762452259</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1109.299421916509</v>
+        <v>1109.299421916508</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -20259,10 +20259,10 @@
         <v>25314</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -20271,22 +20271,22 @@
         <v>25112.75664481348</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>33013.77512679044</v>
+        <v>33013.77512679042</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5875.167457966789</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>629.7844878750775</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>27728.22190465722</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>35937.1267708454</v>
+        <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6144.224276925175</v>
@@ -20601,7 +20601,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -20625,7 +20625,7 @@
         <v>27728.22190465722</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>149710.8391798171</v>
+        <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72515.58812458278</v>
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>20202927.37378142</v>
+        <v>8368076.427010055</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379247</v>
+        <v>68660.92484379245</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -21750,10 +21750,10 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>5485212.825884072</v>
+        <v>2271981.643857308</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>17641.43818058408</v>
+        <v>17641.43818058407</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>4032988.17320214</v>
+        <v>1670468.474107395</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>13115.78537471264</v>
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>2254083.739551511</v>
+        <v>933644.1524769571</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>0</v>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>1494315.767002047</v>
+        <v>618947.3591132739</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>3734.68760967116</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>1323561.141811085</v>
+        <v>548220.5912826977</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>0</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>1103107.309795837</v>
+        <v>456908.3531698731</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>0</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>1058065.19387885</v>
+        <v>438251.8554527781</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>2574.249362596877</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>1006930.011424051</v>
+        <v>417071.6023649913</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>399.0562120303896</v>
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>779093.6061144408</v>
+        <v>322701.4936568689</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>2279.367955575647</v>
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>727757.6503473754</v>
+        <v>301438.0800255401</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3570.123843302602</v>
@@ -22500,7 +22500,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>711913.2607487179</v>
+        <v>294875.3151030191</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>2764.956425043126</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>621162.8750278794</v>
+        <v>257286.3979405418</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>2046.50835444693</v>
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>525331.5278517136</v>
+        <v>217592.9405302955</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>2065.831791566125</v>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>438537.1257698162</v>
+        <v>181642.5964727049</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>1182.728456312894</v>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>406390.5767307102</v>
+        <v>168327.4578174539</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>0</v>
@@ -22861,10 +22861,10 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>370861.5973607908</v>
+        <v>153611.3125163038</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>929.2709615946428</v>
+        <v>929.2709615946429</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -22938,7 +22938,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>361041.4373433588</v>
+        <v>149543.7906155924</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>45.09358878224145</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>315289.0583774526</v>
+        <v>130593.1011030869</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>1062.347281509785</v>
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>203413.7910364303</v>
+        <v>84254.23297366935</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>539.1851296589119</v>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>25300912.53609226</v>
+        <v>10479667.91435774</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>85020.26381129168</v>
@@ -23282,7 +23282,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>6064093.129988029</v>
+        <v>2511754.550882615</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>19275.39740125673</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>4575711.22946696</v>
+        <v>1895265.006288089</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>13646.8462948305</v>
@@ -23449,7 +23449,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>3557791.015706308</v>
+        <v>1473641.249109121</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>0</v>
@@ -23477,13 +23477,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.064847128097</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450652</v>
+        <v>790.7877512450654</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -23492,13 +23492,13 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.838043207603</v>
+        <v>3021.838043207602</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.9119035695702</v>
+        <v>757.9119035695699</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -23510,16 +23510,16 @@
         <v>5957.504189498098</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.086637895055</v>
+        <v>2933.086637895057</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.2309046434759</v>
+        <v>729.2309046434757</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.821732036629</v>
+        <v>9619.821732036631</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -23530,10 +23530,10 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>1511896.178120018</v>
+        <v>626229.1862035578</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>5238.026133777928</v>
+        <v>5238.026133777927</v>
       </c>
     </row>
     <row r="54">
@@ -23564,7 +23564,7 @@
         <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -23579,7 +23579,7 @@
         <v>8427.448628435308</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>1444426.804307502</v>
+        <v>598283.2917250007</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>0</v>
@@ -23639,13 +23639,13 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -23657,25 +23657,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -23692,10 +23692,10 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>1152449.084562691</v>
+        <v>477345.7746709369</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>656.4516549924249</v>
+        <v>656.4516549924248</v>
       </c>
     </row>
     <row r="56">
@@ -23773,7 +23773,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>596905.381986657</v>
+        <v>247238.9156157751</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>4488.014268232506</v>
@@ -23816,34 +23816,34 @@
         <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571055</v>
+        <v>6533.070130571056</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860723</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295336</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961312</v>
+        <v>8093.670157961314</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>429.0106540106552</v>
+        <v>429.0106540106551</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8230.488366920139</v>
+        <v>8230.488366920141</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>406390.5767307102</v>
+        <v>168327.4578174539</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>0</v>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>325090.9386220849</v>
+        <v>134653.0515002718</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>542.4553145801294</v>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>288651.5197327991</v>
+        <v>119559.801072757</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>2350.276413386248</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>203413.7910364303</v>
+        <v>84254.23297366935</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>539.1851296589119</v>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>192828.2644419654</v>
+        <v>79869.69533099154</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>2416.361353419364</v>
@@ -24259,7 +24259,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>147967.3003044499</v>
+        <v>61288.23089533429</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>730.6064652582079</v>
@@ -24287,10 +24287,10 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.13541467506</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>607.4898571432227</v>
@@ -24299,37 +24299,37 @@
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305863</v>
+        <v>30105.74160305862</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966782</v>
+        <v>5875.167457966767</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.7844878750766</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326458</v>
+        <v>32703.15220326457</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6144.224276925182</v>
+        <v>6144.224276925168</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1767.142052340065</v>
+        <v>1767.142052340063</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>655.1214664631962</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>35693.26246439303</v>
+        <v>35693.26246439302</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>136212.5742297695</v>
+        <v>56419.40944428319</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>1420.381992213847</v>
@@ -24407,10 +24407,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -24421,7 +24421,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>134205.7710741676</v>
+        <v>55588.18920231792</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>390.9682489063648</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>119852.3829116568</v>
+        <v>49642.99883914775</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>913.0841014375312</v>
@@ -24589,7 +24589,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>89074.16204079711</v>
+        <v>36894.62333050767</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>71.41468242441327</v>
@@ -24670,7 +24670,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>77576.93271908458</v>
+        <v>32132.45733926579</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>416.2752595267629</v>
@@ -24728,7 +24728,7 @@
         <v>123126.4610400058</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56400.30057805718</v>
+        <v>56400.30057805717</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15913.04608529102</v>
@@ -24737,7 +24737,7 @@
         <v>5035.70598772958</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>131602.601988407</v>
@@ -24751,7 +24751,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>59099.62048988239</v>
+        <v>24479.13274728856</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>655.7778109045844</v>
@@ -24908,7 +24908,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998419</v>
+        <v>6291.051318998418</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
@@ -24920,7 +24920,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215568</v>
+        <v>7755.955719215567</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6402.12610667536</v>
@@ -24935,10 +24935,10 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.85128299104</v>
+        <v>7908.851282991039</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169954</v>
+        <v>6480.947150169952</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
@@ -24950,7 +24950,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283766</v>
+        <v>8025.240261283764</v>
       </c>
     </row>
     <row r="72">
@@ -24993,7 +24993,7 @@
         <v>3.034850177968129</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.99935879958163</v>
+        <v>0.9993587995816298</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -25112,7 +25112,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -25127,7 +25127,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -25176,13 +25176,13 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.409122198132</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174763</v>
+        <v>2374.418161174764</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>535.5877718652724</v>
+        <v>535.5877718652725</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>0</v>
@@ -25194,7 +25194,7 @@
         <v>8643.557255466281</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.307259689338</v>
+        <v>2736.307259689339</v>
       </c>
       <c r="R75" s="131" t="n">
         <v>615.2216261623436</v>
@@ -25206,13 +25206,13 @@
         <v>11995.08614131796</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9438.884141585027</v>
+        <v>9438.884141585026</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058534</v>
+        <v>680.2887679058531</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
@@ -25578,25 +25578,25 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731803</v>
+        <v>2908.033523731805</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -25605,22 +25605,22 @@
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580813</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083913</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.196203083917</v>
       </c>
     </row>
     <row r="82">
@@ -25959,7 +25959,7 @@
         <v>3567.196203083913</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>28545.99954209993</v>
+        <v>28545.99954209994</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -26131,7 +26131,7 @@
         <v>12526.95646477333</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.671517703221</v>
+        <v>4162.67151770322</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.803605389631</v>
@@ -26146,7 +26146,7 @@
         <v>12438.45133966805</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.197362555249</v>
+        <v>4104.197362555251</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.413291097094</v>
@@ -26155,7 +26155,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17645.0619933204</v>
+        <v>17645.06199332039</v>
       </c>
     </row>
     <row r="90">
@@ -26186,7 +26186,7 @@
         <v>7846.477550993603</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
@@ -26201,7 +26201,7 @@
         <v>8428.447987234889</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -26247,13 +26247,13 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -26265,25 +26265,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -26317,7 +26317,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -26332,7 +26332,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         <v>16156</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>14334.76693728304</v>
+        <v>14334.76693728303</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.617170974005</v>
+        <v>3581.617170974007</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>982.7439641763199</v>
@@ -26414,10 +26414,10 @@
         <v>16093.06882680675</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4194.572762452257</v>
+        <v>4194.572762452259</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1109.299421916509</v>
+        <v>1109.299421916508</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -26783,10 +26783,10 @@
         <v>25314</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -26795,22 +26795,22 @@
         <v>25112.75664481348</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>33013.77512679044</v>
+        <v>33013.77512679042</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5875.167457966789</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>629.7844878750775</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>27728.22190465722</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>35937.1267708454</v>
+        <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6144.224276925175</v>
@@ -27125,7 +27125,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -27149,7 +27149,7 @@
         <v>27728.22190465722</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>149710.8391798171</v>
+        <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72515.58812458278</v>
@@ -28197,10 +28197,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>25557925.08718419</v>
+        <v>10804370.66367844</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.10616487113</v>
+        <v>82393.10616487112</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>6422533.964484571</v>
+        <v>2715065.378572194</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>19791.41132971137</v>
@@ -28351,10 +28351,10 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>4143992.791425008</v>
+        <v>1751833.687337102</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>12591.15395972413</v>
+        <v>12591.15395972414</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>2461958.35429605</v>
+        <v>1040769.566684919</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>1933966.374553977</v>
+        <v>817565.9600884158</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>0</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>1715834.184579822</v>
+        <v>725352.6436270382</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>3987.994031430143</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>1233952.866041888</v>
+        <v>521641.8821459876</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>2764.898270390802</v>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>1199872.869442623</v>
+        <v>507234.886499068</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>434.1851303754248</v>
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>1179724.543699668</v>
+        <v>498717.3727010257</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>0</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>913837.2920519767</v>
+        <v>386316.0564068122</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>2448.177946365579</v>
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>834071.5141104009</v>
+        <v>352595.8295801986</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>2957.226786839574</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>628778.1743446308</v>
+        <v>265810.0153935028</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>1964.648020269052</v>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>600610.7686380565</v>
+        <v>253902.5115233766</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>2218.827294049512</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>529738.7911874504</v>
+        <v>223942.0545836161</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>2609.80587903714</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>450607.492488492</v>
+        <v>190490.0478449893</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>1135.419318060378</v>
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>448279.2264421587</v>
+        <v>189505.7954347318</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>1040.245562303857</v>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>434653.9203436769</v>
+        <v>183745.8263843531</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>0</v>
@@ -29462,7 +29462,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>394306.9061492648</v>
+        <v>166689.5084304472</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>47.17150135332714</v>
@@ -29539,7 +29539,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>322539.3286184099</v>
+        <v>136350.445042768</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>1012.746286936093</v>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>260017.5883934369</v>
+        <v>109919.9717698202</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>636.2384529975162</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>30782721.76672266</v>
+        <v>13013103.95386235</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>98089.90734281891</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>7122689.151674757</v>
+        <v>3011049.349833352</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>21621.77584583756</v>
@@ -29852,7 +29852,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>5306337.903622227</v>
+        <v>2243204.070044381</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>14617.76546583174</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>3856892.228329063</v>
+        <v>1630464.644628904</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>0</v>
@@ -30001,13 +30001,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.064847128097</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450652</v>
+        <v>790.7877512450654</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -30016,13 +30016,13 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.838043207603</v>
+        <v>3021.838043207602</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.9119035695702</v>
+        <v>757.9119035695699</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -30034,16 +30034,16 @@
         <v>5957.504189498098</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.086637895055</v>
+        <v>2933.086637895057</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.2309046434759</v>
+        <v>729.2309046434757</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.821732036629</v>
+        <v>9619.821732036631</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -30054,7 +30054,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>2115805.751577129</v>
+        <v>894436.8337570953</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -30103,7 +30103,7 @@
         <v>8427.448628435308</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -30135,7 +30135,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>1367030.230890753</v>
+        <v>577899.0771987148</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>692.1531905196442</v>
@@ -30163,13 +30163,13 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K55" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -30181,25 +30181,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -30216,7 +30216,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>1226751.615084305</v>
+        <v>518597.6215370966</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>3655.504944649816</v>
@@ -30297,10 +30297,10 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>608100.1222868434</v>
+        <v>257068.5648151378</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>4278.46888204873</v>
+        <v>4278.468882048729</v>
       </c>
     </row>
     <row r="57">
@@ -30340,34 +30340,34 @@
         <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571055</v>
+        <v>6533.070130571056</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860723</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295336</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961312</v>
+        <v>8093.670157961314</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>429.0106540106552</v>
+        <v>429.0106540106551</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8230.488366920139</v>
+        <v>8230.488366920141</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>434653.9203436768</v>
+        <v>183745.8263843531</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>0</v>
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>360567.3915007978</v>
+        <v>152426.4483020865</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>557.562695091186</v>
@@ -30540,7 +30540,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>287307.0236172532</v>
+        <v>121456.3219373228</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>2240.542007645244</v>
@@ -30621,7 +30621,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>260017.5883934369</v>
+        <v>109919.9717698202</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>636.2384529975162</v>
@@ -30702,7 +30702,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>216081.7932383239</v>
+        <v>91346.53066926227</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>2461.379047278807</v>
@@ -30783,7 +30783,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>144086.4879025221</v>
+        <v>60911.19750981255</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>378.8783304825305</v>
@@ -30811,10 +30811,10 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.13541467506</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>607.4898571432227</v>
@@ -30823,37 +30823,37 @@
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305863</v>
+        <v>30105.74160305862</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966782</v>
+        <v>5875.167457966767</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.7844878750766</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326458</v>
+        <v>32703.15220326457</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6144.224276925182</v>
+        <v>6144.224276925168</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1767.142052340065</v>
+        <v>1767.142052340063</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>655.1214664631962</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>35693.26246439303</v>
+        <v>35693.26246439302</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30864,7 +30864,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>126749.286111653</v>
+        <v>53582.05972650052</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>905.925522082261</v>
@@ -30931,10 +30931,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -30945,10 +30945,10 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>95640.82184465519</v>
+        <v>40431.25121712827</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>71.94315107435395</v>
+        <v>71.94315107435393</v>
       </c>
     </row>
     <row r="65">
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>68319.76392265428</v>
+        <v>28881.5328536002</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>347.0889752210119</v>
@@ -31113,7 +31113,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>65752.7780362984</v>
+        <v>27796.36389289582</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>662.7618445907182</v>
@@ -31194,7 +31194,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>63419.19559154905</v>
+        <v>26809.86402558196</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>1058.198574957204</v>
@@ -31252,7 +31252,7 @@
         <v>123126.4610400058</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56400.30057805718</v>
+        <v>56400.30057805717</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15913.04608529102</v>
@@ -31261,7 +31261,7 @@
         <v>5035.70598772958</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>27126.77466866458</v>
+        <v>27126.77466866459</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>131602.601988407</v>
@@ -31275,7 +31275,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>50968.78939658258</v>
+        <v>21546.57277698097</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>312.7865385233304</v>
@@ -31432,7 +31432,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998419</v>
+        <v>6291.051318998418</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
@@ -31444,7 +31444,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215568</v>
+        <v>7755.955719215567</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6402.12610667536</v>
@@ -31459,10 +31459,10 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.85128299104</v>
+        <v>7908.851282991039</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169954</v>
+        <v>6480.947150169952</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
@@ -31474,7 +31474,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283766</v>
+        <v>8025.240261283764</v>
       </c>
     </row>
     <row r="72">
@@ -31517,7 +31517,7 @@
         <v>3.034850177968129</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.99935879958163</v>
+        <v>0.9993587995816298</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -31636,7 +31636,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -31651,7 +31651,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -31700,13 +31700,13 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.409122198132</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174763</v>
+        <v>2374.418161174764</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>535.5877718652724</v>
+        <v>535.5877718652725</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>0</v>
@@ -31718,7 +31718,7 @@
         <v>8643.557255466281</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.307259689338</v>
+        <v>2736.307259689339</v>
       </c>
       <c r="R75" s="131" t="n">
         <v>615.2216261623436</v>
@@ -31730,13 +31730,13 @@
         <v>11995.08614131796</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9438.884141585027</v>
+        <v>9438.884141585026</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058534</v>
+        <v>680.2887679058531</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
@@ -32102,25 +32102,25 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731803</v>
+        <v>2908.033523731805</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -32129,22 +32129,22 @@
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580813</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083913</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.196203083917</v>
       </c>
     </row>
     <row r="82">
@@ -32483,7 +32483,7 @@
         <v>3567.196203083913</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>28545.99954209993</v>
+        <v>28545.99954209994</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -32655,7 +32655,7 @@
         <v>12526.95646477333</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.671517703221</v>
+        <v>4162.67151770322</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.803605389631</v>
@@ -32670,7 +32670,7 @@
         <v>12438.45133966805</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.197362555249</v>
+        <v>4104.197362555251</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.413291097094</v>
@@ -32679,7 +32679,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17645.0619933204</v>
+        <v>17645.06199332039</v>
       </c>
     </row>
     <row r="90">
@@ -32710,7 +32710,7 @@
         <v>7846.477550993603</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101696</v>
+        <v>2325.731440101695</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
@@ -32725,7 +32725,7 @@
         <v>8428.447987234889</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.097233451885</v>
+        <v>2681.097233451884</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -32771,13 +32771,13 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>20015.38588163638</v>
+        <v>20015.38588163639</v>
       </c>
       <c r="K91" s="131" t="n">
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -32789,25 +32789,25 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6394149520879</v>
+        <v>890.6394149520878</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20933.99583867971</v>
+        <v>20933.99583867972</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19915.65358131547</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5202998056621</v>
+        <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -32841,7 +32841,7 @@
         <v>176.6473136474771</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>24.08042565817357</v>
+        <v>24.08042565817358</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -32856,7 +32856,7 @@
         <v>184.661213942282</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.7961574208127</v>
+        <v>23.79615742081269</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -32905,10 +32905,10 @@
         <v>16156</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>14334.76693728304</v>
+        <v>14334.76693728303</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.617170974005</v>
+        <v>3581.617170974007</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>982.7439641763199</v>
@@ -32938,10 +32938,10 @@
         <v>16093.06882680675</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4194.572762452257</v>
+        <v>4194.572762452259</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1109.299421916509</v>
+        <v>1109.299421916508</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>0</v>
@@ -33307,10 +33307,10 @@
         <v>25314</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5637.393210158676</v>
+        <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -33319,22 +33319,22 @@
         <v>25112.75664481348</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>33013.77512679044</v>
+        <v>33013.77512679042</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5875.167457966789</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1703.952920346313</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>629.7844878750775</v>
+        <v>629.7844878750784</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>27728.22190465722</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>35937.1267708454</v>
+        <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6144.224276925175</v>
@@ -33649,7 +33649,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -33673,7 +33673,7 @@
         <v>27728.22190465722</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>149710.8391798171</v>
+        <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72515.58812458278</v>
